--- a/extenbooks/XS1302.xlsx
+++ b/extenbooks/XS1302.xlsx
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[internal-decision-record] (2026-05-06): Standard Shaikh-Tonak/Moos formula is NSW = E1 - T1 - T2*LS (E2 excluded). With this formula, ST2 P21 achieves 1959-1997 overlap mean NSW/GDP = 0.013 vs Moos published 0.011. The same E2 exclusion applies to XS1302 (NSW/EC). Mean NSW/EC for overlap period from ST2 is correspondingly higher than NSW/GDP due to EC &lt; GDP. V11 benchmark range [0.008, 0.018] applies to the NSW/GDP ratio (XS1301); XS1302 NSW/EC expected to be roughly 1.5-2x higher given EC/GDP ratio historically ~0.55-0.65.</t>
+          <t>[internal-decision-record] (2026-05-06): Standard Shaikh-Tonak/Moos formula is NSW = E1 - T1 - T2*LS (E2 excluded). With this formula, predecessor-build P21 achieves 1959-1997 overlap mean NSW/GDP = 0.013 vs Moos published 0.011. The same E2 exclusion applies to XS1302 (NSW/EC). Mean NSW/EC for overlap period from predecessor-build is correspondingly higher than NSW/GDP due to EC &lt; GDP. V11 benchmark range [0.008, 0.018] applies to the NSW/GDP ratio (XS1301); XS1302 NSW/EC expected to be roughly 1.5-2x higher given EC/GDP ratio historically ~0.55-0.65.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1426,7 +1426,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NIPA vintage difference between Moos (~2015 pull) and ST2 (2026 pull) affects historical EC values</t>
+          <t>NIPA vintage difference between Moos (~2015 pull) and predecessor-build (2026 pull) affects historical EC values</t>
         </is>
       </c>
     </row>
